--- a/workspace/proyectos/generador-cotizaciones/datos/plantilla-datos.xlsx
+++ b/workspace/proyectos/generador-cotizaciones/datos/plantilla-datos.xlsx
@@ -806,7 +806,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. Guarda el archivo y ejecuta: python generar_cotizacion.py datos/tu-archivo.xlsx</t>
+          <t>4. Guarda el archivo y ejecuta: python3 generar_cotizacion.py datos/tu-archivo.xlsx</t>
         </is>
       </c>
     </row>
